--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -61,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -75,11 +75,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,6 +121,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -543,7 +576,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>吉田 駿成</t>
+          <t>吉田 俊輔</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -554,6 +587,28 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>身体拘束に関する諸課題の最高責任者、家族・医療・行政機関等への対応、指針の改廃の決定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>吉田 麻美</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>事務・総務</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>議事録の作成・保存、記録様式の管理、委員会資料の準備</t>
         </is>
       </c>
     </row>
@@ -563,23 +618,26 @@
           <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>

--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -61,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,39 +75,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,11 +93,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -494,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -612,32 +579,51 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>WIN YADANAR AWNG</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>訪問介護員（ヘルパー代表）</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>現場での拘束・スピーチロックの有無の確認、困りごとの共有、決定事項の現場へのフィードバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>
@@ -646,12 +632,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -587,43 +587,65 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>松村 知恵</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>訪問介護員</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>現場での拘束・スピーチロックの有無の確認、事例の共有</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>委員</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>WIN YADANAR AWNG</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>訪問介護員（ヘルパー代表）</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>現場での拘束・スピーチロックの有無の確認、困りごとの共有、決定事項の現場へのフィードバック</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
+          <t>【開催】年1回以上定期的に開催（感染症対策委員会・虐待防止委員会と同日に開催：6月・11月）。身体拘束の検討が必要なとき、適切な手続きによらない拘束が判明したとき等は随時開催する。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
+          <t>【参加】必要に応じて、サービス提供責任者・当該利用者の担当訪問介護員・居宅介護支援事業所（ケアマネジャー）・主治医等の参加を求める。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>【記録】議事録を委員会ごとに作成し、全職員に周知のうえ5年間保存する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>根拠：「身体拘束廃止に関する指針」3（1）</t>
         </is>
@@ -634,8 +656,8 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>

--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -592,12 +592,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>訪問介護員</t>
+          <t>看護職</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>現場での拘束・スピーチロックの有無の確認、事例の共有</t>
+          <t>医療的な視点からの助言、利用者の心身状況の評価、事例の共有</t>
         </is>
       </c>
     </row>

--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>WIN YADANAR AWNG</t>
+          <t>WIN YADANAR AUNG</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">

--- a/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
+++ b/output/身体拘束適正化委員会_委員名簿_いいかいご.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>吉田 俊輔</t>
+          <t>吉田 駿成</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
